--- a/скрипт Блиц-запись холодный звонок.xlsx
+++ b/скрипт Блиц-запись холодный звонок.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Скрипт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отработка возражений" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Памятка по продукту" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры для звонка" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Скрипт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Отработка возражений" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Тарифы для звонка" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Примеры для звонка" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,55 +111,11 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D7DE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D7DE"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -179,8 +135,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,35 +500,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ»  |  Цель — записать клиента на демонстрацию сервиса (15–20 минут)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="204" customHeight="1">
+          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ»  |  Цель — выйти на ЛПР и записать на демонстрацию сервиса (15–20 минут)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="220" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Как идёт звонок (для себя, клиенту не читать): сначала знакомимся и коротко говорим, кто мы → задаём вопросы и слушаем → своими словами повторяем, что услышали → рассказываем только то, что откликнулось клиенту → если нужно, приводим пример → приглашаем на демонстрацию. В звонке не продаём тариф — договариваемся о встрече.</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="8" t="n"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Логика звонка (себе, не читать клиенту): новый заход — бесплатный старт и самостоятельная онлайн-запись. Сначала находим ЛПР → коротко говорим про сервис → спрашиваем, как сейчас принимают запись → под боль рассказываем про Старт 0 ₽ / модули / Управление / Премиум → приглашаем на демонстрацию. В звонке не продаём подписку — продаём интерес к демонстрации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>1. Первичный контакт / приветствие и презентация компании</t>
@@ -587,13 +539,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Добрый день, [Имя Отчество]! Меня зовут [имя], компания «Форус». Я попал(а) к владельцу или руководителю [салона / автомойки / школы / студии]?</t>
+          <t>Добрый день! Меня зовут [имя], я из компании «Форус». Мы предлагаем вам посотрудничать с нами и бесплатно установить наше новое приложение для самостоятельной онлайн-записи клиентов. Оно подключается куда угодно: в 2ГИС, на ваш сайт или в социальные сети. С кем могу обсудить вопрос сотрудничества?</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -602,15 +553,14 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Подскажите, пожалуйста, с кем лучше поговорить про запись клиентов и расписание? Как к человеку обратиться и когда удобнее перезвонить?</t>
+          <t>Подскажите, пожалуйста, с кем лучше обсудить запись клиентов и расписание? Как к человеку обратиться и когда удобно перезвонить?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Записываем ФИО, роль и время — перезваниваем</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+          <t>Фиксируем ФИО, роль, время → перезвон</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="3" t="inlineStr"/>
@@ -621,7 +571,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Скажите, у вас есть две-три минуты? Хочу коротко рассказать, кто мы, и уточнить, как у вас сейчас устроена запись клиентов.</t>
+          <t>Отлично. У вас буквально две-три минуты? Хочу коротко показать идею и уточнить, как у вас сейчас устроена запись клиентов.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -629,26 +579,28 @@
           <t>Если сейчас некогда — договариваемся о перезвоне с конкретным временем</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Презентация компании</t>
+    </row>
+    <row r="6" ht="108" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2. Короткий рассказ про сервис</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Наша компания занимается автоматизацией записи клиентов и предлагает для этого удобный сервис — «Блиц-запись». Мы из группы компаний «Форус», работаем с бизнесом в сфере услуг.</t>
+          <t>«Блиц-запись» — наш сервис для самостоятельной онлайн-записи. Клиент сам выбирает услугу и время — с сайта, из 2ГИС, Яндекс Карт или соцсетей. Можно начать бесплатно на тарифе «Старт»: календарь, онлайн-запись, прайс и до пяти сотрудников — без абонентской платы. Если понадобится больше — подключаете только нужные инструменты или берёте полный тариф.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Два предложения — и сразу к вопросам. Не растягивать</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>Не больше 20–25 секунд. Сразу к вопросам</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="3" t="inlineStr"/>
@@ -667,39 +619,33 @@
           <t>Открытый вопрос — дальше говорит клиент</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="44" customHeight="1">
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2. Сбор потребности (больше говорит клиент)</t>
+          <t>3. Сбор потребности</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Тип вопроса</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>ОСНОВНЫЕ ВОПРОСЫ (салоны, автомойки, курсы, студии, ИП)</t>
+          <t>Вопросы</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>САЛОН КРАСОТЫ / БАРБЕРШОП</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>АВТОМОЙКА / АВТОУСЛУГИ / КУРСЫ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>Что фиксируем</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2.1 Как записывают сейчас</t>
+          <t>3.1 Как записывают</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -709,24 +655,19 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Клиенты к вам чаще звонят, пишут в мессенджеры, приходят из соцсетей — или уже есть запись через интернет?</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Через что чаще всего записываются — соцсети, мессенджер или звонок администратору?</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка: запись идёт через администратора, сайт или приложение? Курсы: как ученики выбирают время занятия?</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>Клиенты к вам чаще звонят, пишут в мессенджеры, приходят из соцсетей — или уже есть онлайн-запись?</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Канал записи</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2.2 Кто ведёт расписание</t>
+          <t>3.2 Кто ведёт расписание</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -736,24 +677,19 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>А кто у вас этим занимается — вы сами, администратор или мастер?</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Сколько мастеров в смене? Кто разруливает, если времена пересеклись?</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка: сколько постов и кто распределяет машины? Курсы: кто ведёт расписание преподавателей?</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Кто этим занимается — вы сами, администратор или мастер?</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Кто ЛПР / кто работает с записью</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2.3 Чем пользуются сейчас</t>
+          <t>3.3 Чем пользуются</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -763,25 +699,20 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Вы сейчас чем-то пользуетесь для записи — тетрадью, таблицей, «Юклиентс», «Дикиди» или чем-то ещё?
-Если назвали сервис: а что в нём нравится, а что раздражает?</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Стоимость вашего сервиса зависит от числа мастеров? Это для вас ощутимо?</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка: удобно ли в текущем сервисе работать с постами в час пик? Курсы: можно ли записывать и на группы, и на индивидуальные занятия?</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>Чем сейчас пользуетесь — тетрадь, таблица, «Юклиентс», «Дикиди» или что-то ещё?
+Если назвали сервис: что в нём удобно, а что мешает или кажется лишним?</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Текущий инструмент и боли</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2.4 Где теряются клиенты</t>
+          <t>3.4 Потери заявок</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -791,79 +722,65 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Бывает такое, что в час пик клиент не может дозвониться, пишет в мессенджер — и запись куда-то пропадает? Как часто так случается?</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Бывают ли двойные записи на одного мастера или «дыры» в расписании, которые сложно закрыть?</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка: что происходит в час пик — очередь, путаница по постам? Курсы: часто ли ученики забывают про занятие?</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
+          <t>Бывает, что в час пик клиент не дозванивается, пишет в мессенджер — и запись пропадает? Как часто так бывает?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Потери и хаос</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2.5 Неявки</t>
+          <t>3.5 Онлайн-запись и каналы</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Закрытый → открытый</t>
+          <t>Закрытый / открытый</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Вы напоминаете клиентам о визите заранее?
-Если нет: а неявки сильно бьют по загрузке?</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Какой примерно процент людей не приходит без предупреждения?</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка: из-за неявок пост простаивает? Курсы: как отрабатываете пропуски?</t>
+          <t>Клиенты могут сами записаться с сайта, из 2ГИС или соцсетей — или всё идёт только через администратора?
+Было бы удобно, если бы запись шла сама, без звонка?</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Готовность к самостоятельной онлайн-записи</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2.6 Запись вечером и в выходные</t>
+          <t>3.6 Неявки</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Закрытый</t>
+          <t>Закрытый → открытый</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Клиенты часто пишут или звонят вечером и в выходные, когда администратора уже нет?</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Было бы удобно, если бы клиент сам выбирал мастера и время, даже когда вас нет на месте?</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка: принимали бы заявки круглосуточно, чтобы ночные обращения не терялись?</t>
+          <t>Вы напоминаете клиентам о визите?
+Если нет: а неявки сильно бьют по загрузке?</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Неявки / напоминания</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2.7 База клиентов</t>
+          <t>3.7 Главная боль</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -873,120 +790,95 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>А база клиентов и история визитов у вас где хранится — в телефоне, в тетради, в сервисе?</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Можете быстро понять, кто давно не был, и напомнить о себе?</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Насколько важно видеть историю по клиенту — услуги, визиты, для мойки ещё и по автомобилю?</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>Если честно: что в записи и расписании сейчас больше всего отнимает время или нервы?</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Главная боль</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2.8 Что больше всего мешает</t>
+          <t>3.8 Повтор услышанного</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Открытый</t>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Если честно: что в записи и расписании сейчас больше всего отнимает время или нервы?</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Если бы можно было поменять одну вещь в записи клиентов — что бы это было?</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Что для вас важнее: меньше звонков администратору, меньше простоев или чтобы загрузку было видно?</t>
+          <t>Правильно понимаю: сейчас у вас [как записывают], больше всего мешает [боль], и важно [что хочет получить]. Верно?</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждение перед презентацией</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2.9 Насколько тема сейчас живая</t>
+          <t>4. Рассказ о «Блиц-записи» под боль клиента</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Закрытый</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Вы эту тему сейчас как-то смотрите, или она есть, но руки не доходят?</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Если найдётся вариант проще и выгоднее текущего — готовы сравнить?</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Если за 15 минут покажем, как это устроено у похожих бизнесов — интересно будет посмотреть?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
+          <t>Правило</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Берём 2–3 пункта из ответов. Прайс целиком не читаем. Акцент — бесплатный старт и самостоятельная онлайн-запись.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2.10 Повторяем, что услышали</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+          <t>Если теряют заявки / много звонков</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Говорим</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Правильно понимаю: сейчас у вас [как записывают], больше всего мешает [боль клиента], и важно [что хочет получить]. Верно?</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Ждём «да». Дальше говорим только про то, что откликнулось — не про весь сервис сразу</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="44" customHeight="1">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Как раз для этого и делали: клиент сам записывается онлайн — с сайта, из 2ГИС, Яндекс Карт, соцсетей. Заявка сразу в календарь, без накладок. Администратор меньше сидит на телефоне.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="76" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>3. Рассказ о «Блиц-записи» (коротко, под боль клиента)</t>
+          <t>Если дорого / не готовы платить сразу</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Правило</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Берём два-три пункта из ответов клиента. Прайс не читаем. С текущим сервисом не спорим — предлагаем посмотреть на демонстрации.</t>
+          <t>Говорим</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Можно начать бесплатно: тариф «Старт» — 0 рублей в месяц. Календарь, онлайн-запись, прайс, до пяти сотрудников, один филиал. Абонентской платы нет. Когда понадобится аналитика, зарплата, лояльность или Telegram-бот — подключаете только нужное или берёте полный тариф.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="76" customHeight="1">
+    </row>
+    <row r="20" ht="44" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Если теряют заявки или много звонков</t>
+          <t>Если путаница в расписании</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -996,16 +888,15 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Как раз для этого и делали «Блиц-запись»: клиент сам записывается через интернет — с сайта, из соцсетей, с карт. Заявка сразу падает в календарь администратора, без накладок. Меньше пропущенных звонков — меньше потерянных клиентов.</t>
+          <t>Всё расписание в одном месте. Система не даёт задвоить запись. На «Управлении» ещё графики сотрудников и контроль загрузки.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Если путаница в расписании</t>
+          <t>Если нужна база / возврат клиентов</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1015,16 +906,15 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Всё расписание в одном месте: по сотрудникам, кабинетам, постам. Система не даёт записать двух клиентов на одно и то же время. Загрузку видно сразу.</t>
+          <t>На «Старте» есть база клиентов. Если нужна история визитов, выгрузка, аналитика и система лояльности — это уже в доп. инструментах или в тарифе «Управление».</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+    </row>
+    <row r="22" ht="76" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Если неявки и «забыл прийти»</t>
+          <t>Если хотят «всё под ключ» и бренд</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1034,230 +924,107 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Сервис сам напоминает клиенту о визите — смс или сообщение в мессенджере. По нашему опыту, простоев из‑за неявок становится заметно меньше — примерно на треть.</t>
+          <t>Тогда смотрим «Премиум»: персональный менеджер, брендирование кабинета и страницы записи, размещение в витрине, запуск под ключ, подключение каналов привлечения и аналитика записей из 2ГИС, Яндекс Карт, сайта и соцсетей.</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="44" customHeight="1">
+    </row>
+    <row r="23" ht="76" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Если база размазана</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+          <t>5. Приглашение на демонстрацию</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Говорим</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Внутри есть клиентская база: контакты, история визитов, комментарии. Можно быстро найти, кто давно не был, и вернуть человека.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="76" customHeight="1">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Давайте я просто покажу, как это выглядит. За 15–20 минут пройдёмся по онлайн-записи, календарю и бесплатному старту — уже на вашем формате. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Всегда даём выбор из двух вариантов времени</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Если дорого или слишком много лишнего</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+          <t>Если «надо подумать»</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Говорим</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>У нас цена не растёт от числа мастеров — платите за сервис, а не «за каждого человека». Многое из больших систем малому бизнесу просто не нужно. Если переходите с другого сервиса — даём до шести месяцев в подарок, базу переносим сами.</t>
+          <t>Понимаю. Как раз поэтому и предлагаю короткую демонстрацию — посмотрите глазами, особенно бесплатный «Старт», и уже после будет понятнее. Давайте поставим 15 минут на [день]?</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25" ht="76" customHeight="1">
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Если нужен общий рассказ</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+          <t>Фиксация</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Говорим</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>«Блиц-запись» — это запись клиентов через интернет, расписание, база и напоминания в одном окне. Работает с компьютера, планшета и телефона, ничего ставить не нужно. Мы помогаем подключить и настроить — услуги, сотрудников, ссылки на запись.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="44" customHeight="1">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Хорошо. Куда удобнее отправить ссылку — на почту или в мессенджер? Подтверждаем: [дата], [время], демонстрация «Блиц-запись», минут 15–20. Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>После звонка: письмо со ссылкой + задача в CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>4. Пример внедрения (по сегменту, если нужно)</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Когда говорить</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Только если клиент сомневается или спрашивает «а у кого это уже стоит». В каждый звонок не вставляем.</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="92" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Салон «Луна»</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+          <t>6. Если демонстрацию сейчас не ставят</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Говорим</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Салон красоты «Луна» ушёл с «Юклиентс» к нам. Мы перенесли около двух тысяч клиентов и около ста услуг. За год они стали платить примерно на треть меньше — было 36 360 рублей, стало 22 800, плюс шесть месяцев в подарок за переход. Через полтора месяца оформили годовую подписку.</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="92" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Автомойка «Элис»</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Автомоечный комплекс «Элис» в Иркутске — восемь постов, около двух тысяч записей в месяц — тоже ушёл с «Юклиентс». Сделали им удобный календарь, быструю запись для часа пик, расчёт зарплат, подключили кассу. Базу перенесли без потерь, дали шесть месяцев в подарок — и они остались на годе.</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29" ht="76" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>5. Приглашение на демонстрацию (главная цель звонка)</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Давайте я вам просто покажу, как это выглядит. За 15–20 минут пройдёмся по календарю, записи и напоминаниям — уже на вашем формате. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Даём выбор из двух вариантов. Не спрашиваем «интересно ли» — спрашиваем «когда удобно»</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Если говорит «надо подумать»</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Понимаю. Как раз поэтому и предлагаю короткую демонстрацию — посмотрите глазами, и уже после будет понятнее, есть ли о чём думать. Давайте поставим 15 минут на [день]?</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="76" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Закрепляем договорённость</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Хорошо. Куда удобнее отправить ссылку — на почту или в мессенджер? Тогда подтверждаем: [дата], [время], демонстрация «Блиц-запись», минут 15–20. Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>После звонка: письмо со ссылкой + задача в CRM (см. регламент после записи на демонстрацию)</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="76" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>6. Если демонстрацию сейчас не ставят</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Хорошо, настаивать не буду. Зафиксирую, что для вас важно: [боль]. Могу скинуть короткое коммерческое предложение на почту и созвониться [день / время] — сравним с тем, как у вас сейчас. Какая почта удобнее?</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Следующий шаг обязателен: письмо, перезвон или материал. Звонок без следующего шага — потерянный контакт</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
-    </row>
-    <row r="34" ht="172" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>На заметку: тариф в холодном звонке не продаём; с «Юклиентс» и «Дикиди» не спорим — зовём сравнить на демонстрации; дольше 40–50 секунд подряд не говорим; после вопросов — пауза и слушаем; цену называем только если спросили (см. лист «Памятка по продукту»).</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="8" t="n"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Хорошо, настаивать не буду. Зафиксирую, что для вас важно: [боль]. Могу скинуть короткое описание тарифов — там есть бесплатный «Старт» — и созвониться [день / время]. Какая почта удобнее?</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Следующий шаг обязателен: письмо / перезвон / материал</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="156" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>На заметку: в холодном звонке не продаём «Управление»/«Премиум» в лоб — ведём через бесплатный старт и демонстрацию; с «Юклиентс»/«Дикиди» не спорим; дольше 40–50 секунд подряд не говорим; цену полного тарифа называем только если спросили.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1269,20 +1036,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (микро- и малый бизнес, ИП: салоны, автомойки, курсы, студии)</t>
-        </is>
-      </c>
+          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (новый заход: бесплатный Старт + онлайн-запись)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1297,11 +1066,11 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Зачем</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Цель</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Мне некогда / занят</t>
@@ -1309,16 +1078,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Понимаю, не буду вас долго держать. Предлагаю 15 минут демонстрации в удобное время — просто посмотрите, есть ли смысл вообще к этому возвращаться. Когда спокойнее: утром или вечером?</t>
+          <t>Понимаю, не буду долго держать. Предлагаю 15 минут демонстрации — покажу, как выглядит бесплатная онлайн-запись. Когда спокойнее: утро или вечер?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Договориться о времени демонстрации</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="76" customHeight="1">
+          <t>Слот на демонстрацию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Нас всё устраивает</t>
@@ -1326,67 +1095,67 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Хорошо, значит у вас уже порядок — это плюс. Часто к нам смотрят не потому, что «всё плохо», а чтобы администратор меньше сидел на телефоне и записи вечером не терялись. Давайте за 15 минут сравните с тем, как у вас сейчас — вдруг пригодится.</t>
+          <t>Хорошо, значит процесс уже есть. Часто смотрят «Блиц», чтобы клиент записывался сам с 2ГИС и сайта, а администратор меньше сидел на телефоне. И начать можно бесплатно. Давайте за 15 минут сравните с тем, как у вас сейчас?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Снять «нас всё устраивает» и вызвать интерес</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="92" customHeight="1">
+          <t>Интерес к бесплатному старту</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>У нас уже есть «Юклиентс» / «Дикиди» / другой сервис</t>
+          <t>Уже есть другой сервис</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Значит, с записью через интернет вы уже работаете — отлично. К нам часто приходят из‑за цены «за мастера», тяжёлого интерфейса или когда поддержка не слышит. Салон «Луна» и мойка «Элис» как раз переехали с «Юклиентс»: базу перенесли мы, плюс до шести месяцев в подарок. Могу коротко показать разницу на демонстрации.</t>
+          <t>Значит, с онлайн-записью вы уже знакомы. К нам часто приходят из‑за цены и лишнего функционала. У нас можно начать с нуля рублей и подключать только нужное. Могу коротко показать разницу на демонстрации.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Не уговаривать бросить сервис — предложить сравнить</t>
+          <t>Сравнить, не спорить</t>
         </is>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Это дорого</t>
+          <t>Это платно / дорого</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Давайте по цифрам. Ориентир — от 1 500 рублей в месяц при оплате на два года, на год — около 1 900; от числа мастеров цена не растёт. Салон «Луна», например, экономит порядка 13 500 рублей в год относительно прошлого сервиса. На демонстрации прикинем под вашу схему — часто выходит дешевле привычного.</t>
+          <t>Как раз можно начать бесплатно: тариф «Старт» — 0 рублей в месяц. Календарь, онлайн-запись, прайс, до пяти сотрудников. Полный тариф «Управление» — от 1 900 рублей в месяц при оплате за год. На демонстрации покажем оба варианта.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Увести от эмоции к сравнению на демонстрации</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
+          <t>Снять страх цены через Старт 0 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>У нас маленький бизнес / я один</t>
+          <t>Маленький бизнес / я один</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Как раз для небольшого бизнеса и делали: запись, календарь, база, напоминания — без лишнего «для сетей». Если поток небольшой, есть оплата по факту записей через интернет, баланс от 1 000 рублей. На демонстрации покажем простой сценарий именно под вас.</t>
+          <t>Для небольшого бизнеса как раз «Старт»: без абонентки, до пяти сотрудников. Если чего-то не хватит — подключаете отдельные инструменты, а не весь пакет сразу.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Убрать страх «это для крупных»</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="76" customHeight="1">
+          <t>Подтвердить, что подходит микробизнесу</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Клиенты всё равно звонят</t>
@@ -1394,165 +1163,97 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Часть клиентов всегда будет звонить — это нормально. Сервис забирает тех, кто готов записаться сам: вечером, с работы, из соцсети. По практике больше 40% записей может приходить через интернет. Администратор при этом тоже может записывать, как раньше.</t>
+          <t>Часть будет звонить — это нормально. Задача сервиса — забрать тех, кто готов записаться сам с карты, сайта или соцсети. Администраторская запись никуда не девается.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Показать, что оба способа работают вместе</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>Оба канала вместе</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Боимся переносить базу</t>
+          <t>Нет сайта</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Перенос берём на себя. В наших внедрениях переносили тысячи контактов и услуги, работа при этом не останавливалась. Сначала смотрите в тестовом доступе, платите, когда будете готовы.</t>
+          <t>Сайт не обязателен. Онлайн-запись ставят в 2ГИС, Яндекс Карты, соцсети и мессенджер — клиент переходит по ссылке и выбирает время.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Снять страх потери данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="76" customHeight="1">
+          <t>Убрать барьер «нужен сайт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Не хотим ничего внедрять / сложно</t>
+          <t>Боимся переносить базу / сложно</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Мы сами подключаем и настраиваем: услуги, расписание, сотрудников, ссылки на запись. Вам не нужно разбираться с нуля. На демонстрации увидите, как выглядит обычный день администратора — обычно это проще тетради и переписки в чатах.</t>
+          <t>На «Старте» помогаем с переносом и настройкой прайса. На «Премиуме» — запуск под ключ и персональный менеджер. На демонстрации покажем, как это выглядит.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Показать, что мы сопровождаем запуск</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1">
+          <t>Снять страх внедрения</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Пришлите на почту / в мессенджер</t>
+          <t>Пришлите на почту</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Конечно, направлю. Чтобы не слать лишнее, уточню: что сейчас больше всего мешает — пропущенные заявки, неявки или цена текущего сервиса? … Спасибо. И давайте сразу поставим 15 минут — так материал не потеряется в почте. Когда удобно?</t>
+          <t>Конечно, направлю. Чтобы не слать лишнее: что сейчас больнее — звонки, неявки или цена текущего сервиса? … И давайте сразу поставим 15 минут — так материал не потеряется. Когда удобно?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Не оставлять только на «пришлите»</t>
+          <t>Не оставить только на «пришлите»</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Надо посоветоваться с партнёром / администратором</t>
+          <t>Надо посоветоваться</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Логично. Давайте сразу пригласим его или её на демонстрацию — за те же 15–20 минут оба посмотрите и быстрее решите. Когда вам двоим удобно?</t>
+          <t>Логично. Давайте сразу пригласим партнёра или администратора на демонстрацию. Когда вам обоим удобно?</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Пригласить на демонстрацию ЛПР и того, кто влияет</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="76" customHeight="1">
+          <t>Демо с ЛПР и влияющим</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Работаем в тетради / таблице</t>
+          <t>Кто вы такие</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Тетрадь понятная, спорить не буду. Обычно она ломается в час пик: накладки, потерянные сообщения, нет напоминаний. «Блиц» — тот же журнал, только в телефоне и на компьютере, плюс запись через интернет. Посмотрите 15 минут — если тетрадь удобнее, так и останетесь.</t>
+          <t>Мы из группы компаний «Форус». «Блиц-запись» — наш сервис онлайн-записи для бизнеса в сфере услуг. Можно начать бесплатно и посмотреть на демонстрации.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Уважить привычку и пригласить на демонстрацию</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Нет сайта — нам это не нужно</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Сайт не обязателен. Ссылку на запись ставят в мессенджер, соцсети, на карты — клиент переходит и выбирает время. Многие ИП так и начинают.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Убрать барьер «нужен сайт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Кто вы такие / не доверяем</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Мы из группы компаний «Форус» — больше 30 лет на рынке, официальный партнёр фирмы «1С». «Блиц-запись» — наша разработка, сервис в реестре российского программного обеспечения. Рядом живая поддержка, не бросаем после оплаты. На демонстрации покажем кабинет и примеры салонов и моек.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Укрепить доверие</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Сейчас не сезон / потом</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Как раз между сезонами удобнее спокойно всё настроить, чтобы к пику уже принимать заявки круглосуточно. Давайте найдём короткое окно на этой неделе — потом времени будет ещё меньше.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Связать с подготовкой к сезону</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>А какая цена?</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Ориентир такой: 2 500 рублей в месяц при коротком сроке; на год — около 1 900; на два года — от 1 500. Точнее посчитаем на демонстрации под ваш сценарий: сколько людей работает, есть ли уже сервис. Могу забронировать 15 минут — и сразу прикинем.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>От цены — к демонстрации</t>
+          <t>Доверие + демо</t>
         </is>
       </c>
     </row>
@@ -1570,203 +1271,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПАМЯТКА МЕНЕДЖЕРУ — «БЛИЦ-ЗАПИСЬ» (себе перед звонком; клиенту не читать)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+          <t>ТАРИФЫ «БЛИЦ-ЗАПИСЬ» ДЛЯ ХОЛОДНОГО ЗВОНКА  |  Заход: начните бесплатно → нужные инструменты → всё в одном тарифе</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+    </row>
+    <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Тема</t>
+          <t>Тариф</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Содержание</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Что входит / как говорить</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="124" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Продукт</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>«Блиц-запись» — сервис для записи клиентов, расписания, клиентской базы и загрузки сотрудников в одном окне. Разработка научно-производственной фирмы «Форус».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
+          <t>Старт</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>0 ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Всё нужное, чтобы принимать онлайн-записи и вести расписание без абонентской платы.
+Входит: календарь и онлайн-запись; база клиентов без истории и выгрузки; прайс-лист; помощь с переносом и настройкой прайса; до 5 сотрудников; 1 филиал; уведомления PWA и Windows; базовое размещение в витрине партнёров.
+Фраза: «Можно начать бесплатно — без абонентской платы.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="140" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Для кого</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Салоны красоты и барбершопы; автомойки; клиники; курсы и учебные центры; фитнес и студии; частные специалисты; любой бизнес по предварительной записи.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+          <t>Модули к «Старту»</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Подключаются отдельно</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Расширяйте тариф под себя — только то, что нужно:
+операционная и финансовая аналитика; график работы сотрудников; автоматический расчёт зарплаты; полная база клиентов с историей, выгрузкой и аналитикой; Telegram-бот с уведомлениями и быстрым управлением записями; система лояльности: скидки, абонементы и сертификаты.
+Фраза: «Не обязательно брать всё сразу — подключаете только нужные инструменты.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="124" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Сегмент звонка</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Микро- и малый бизнес, ИП.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1 900 ₽/мес при оплате за год
+22 800 ₽ в год
+или 2 100 ₽ при ежемесячной оплате
+Экономия за год — 2 400 ₽</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Весь бизнес в цифрах и под контролем.
+Всё из «Старта» + все доп. инструменты:
+контроль выручки, загрузки и простоев; удалённая аналитика; графики и зарплата; история посещений; лояльность; Telegram-бот.
+Фраза: «Если нужно всё сразу — тариф „Управление“, выгоднее при оплате за год.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Чем сильны</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Простая запись, расписание и база; цена не зависит от числа мастеров; помогаем внедрить; переход с других сервисов берём на себя; до шести месяцев в подарок при переходе; реестр российского программного обеспечения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Что умеет</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Запись через интернет круглосуточно; календарь администратора; загрузка по сотрудникам, кабинетам, постам; напоминания; база и история; анализ загрузки; роли; связь с телефонией, CRM, кассой, «1С», мессенджерами; работает в браузере.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Цифры</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Больше 40% записей через интернет; больше 19% записей за первые 14 дней; примерно на 31% меньше простоев из‑за неявок; 64% автовладельцев выбирают запись через интернет (опрос 2024 года).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Тарифы</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>3 месяца — 2 500 ₽/мес; 6 месяцев — 2 300 ₽/мес; 1 год — 1 900 ₽/мес; 2 года — 1 500 ₽/мес. Есть оплата за фактические записи через интернет (баланс от 1 000 ₽). При переходе с другого сервиса — до шести месяцев дополнительно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Пробный период</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>14 дней бесплатно / тестовый доступ — обычно после демонстрации.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Цель звонка</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Записать на демонстрацию 15–20 минут. Тариф в холодном звонке не продаём.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Контакты</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>+7 992 117-29-16 · vmoskvitina@forus.ru · blitz@forus.ru · блиц-запись.рф · «Форус»: forus.ru, +7 (3952) 78-00-00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Пример «Луна»</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Салон, переход с «Юклиентс». ~2000 клиентов, 6 мастеров, ~100 услуг. Экономия около 37% (36 360 → 22 800 ₽/год) + 6 месяцев в подарок. Год оплатили 07.08.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Пример «Элис»</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка, 8 постов, ~2000 записей/мес. Переход с «Юклиентс». Календарь, быстрая запись, зарплаты, касса. +6 месяцев. Год с апреля 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>После записи на демонстрацию</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Письмо со ссылкой → напоминание за день → за час → менеджер на встрече → обратная связь в течение трёх дней.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Чего не делать</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Не читать весь функционал; не спорить с конкурентами; не давить ценой; не заканчивать без следующего шага; не говорить больше клиента.</t>
+          <t>Премиум</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2 067 ₽/мес при оплате за год
+24 800 ₽ в год
+или 2 300 ₽ при ежемесячной оплате</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>«Блиц-запись», полностью настроенная под бизнес и бренд.
+Всё из «Управления» + персональный менеджер; полное брендирование кабинета и страницы записи; расширенное XL-размещение в витрине; настройка и запуск под ключ; подключение каналов привлечения; UTM и аналитика записей из 2ГИС, Яндекс Карт, сайта и соцсетей.
+Фраза: «Если нужен запуск под ключ и бренд — смотрим „Премиум“.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="188" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>В холодном звонке опираемся на формулу КП: «Начните бесплатно, подключайте только нужные инструменты или получите все возможности сервиса в одном тарифе.» Детали тарифов — на демонстрации.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1778,23 +1409,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПРИМЕРЫ ВНЕДРЕНИЯ — коротко вставить в разговор</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+          <t>ПРИМЕРЫ ВНЕДРЕНИЯ — коротко в разговор</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Пример</t>
@@ -1807,16 +1441,16 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Боль до перехода</t>
+          <t>Боль до</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Что сказать</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Фраза</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Салон «Луна»</t>
@@ -1829,16 +1463,16 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>«Юклиентс» дорого (цена от числа мастеров), лишний функционал, медленно грузится</t>
+          <t>Дорогой сервис, лишний функционал</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>«Перенесли две тысячи клиентов, экономия около трети в год, плюс шесть месяцев за переход. Салон остался на годе.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+          <t>«Перенесли базу под ключ, снизили годовые затраты, салон остался на подписке.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Комплекс «Элис»</t>
@@ -1846,34 +1480,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Автомойка (8 постов)</t>
+          <t>Автомойка</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Дорого (около 120 тысяч в год), ошибки в зарплатах, не подключили телефонию, тяжёлый интерфейс</t>
+          <t>Дорого, тяжёлый интерфейс, нужны доработки</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>«Сделали календарь под восемь постов, быструю запись для часа пик, зарплаты и кассу. Базу сохранили. Плюс шесть месяцев в подарок.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Когда вставлять: назвал конкурента — пример перехода; боится переноса — «переносим сами»; жалуется на цену — цифры «Луны»; автобизнес — «Элис». Одного примера за звонок хватает.</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="n"/>
+          <t>«Сделали календарь под посты и пик, базу сохранили, дали бонус за переход.»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/скрипт Блиц-запись холодный звонок.xlsx
+++ b/скрипт Блиц-запись холодный звонок.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Скрипт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Отработка возражений" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Тарифы для звонка" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Примеры для звонка" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ветка Дикиди" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Отработка возражений" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Тарифы для звонка" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,33 +500,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ»  |  Цель — выйти на ЛПР и записать на демонстрацию сервиса (15–20 минут)</t>
+          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ»  |  Ветка для клиентов на «Дикиди»  |  Цель — выйти на ЛПР и записать на демонстрацию</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
     </row>
-    <row r="2" ht="220" customHeight="1">
+    <row r="2" ht="140" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Логика звонка (себе, не читать клиенту): новый заход — бесплатный старт и самостоятельная онлайн-запись. Сначала находим ЛПР → коротко говорим про сервис → спрашиваем, как сейчас принимают запись → под боль рассказываем про Старт 0 ₽ / модули / Управление / Премиум → приглашаем на демонстрацию. В звонке не продаём подписку — продаём интерес к демонстрации.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="92" customHeight="1">
+          <t>Логика (себе): заход про бесплатный сервис → спрашиваем, чем пользуются → если «Дикиди», уточняем, сталкивались ли с проблемами → ветка «да» или «нет» → рассказ про бесплатный сервис и хранение в Иркутске → демонстрация.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="76" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>1. Первичный контакт / приветствие и презентация компании</t>
@@ -539,10 +539,14 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Добрый день! Меня зовут [имя], я из компании «Форус». Мы предлагаем вам посотрудничать с нами и бесплатно установить наше новое приложение для самостоятельной онлайн-записи клиентов. Оно подключается куда угодно: в 2ГИС, на ваш сайт или в социальные сети. С кем могу обсудить вопрос сотрудничества?</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
+          <t>Здравствуйте! Меня зовут [имя], группа компаний «Форус». Мы автоматизируем бизнес и онлайн-запись. Звоню по вопросу сотрудничества: предлагаем бесплатный сервис для онлайн-записи клиентов. Подскажите, чем вы сейчас пользуетесь?</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Ждём ответ. Если «Дикиди» — этап 2. Если другой сервис / тетрадь — фиксируем и идём в сбор потребности</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="3" t="inlineStr"/>
@@ -553,37 +557,41 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Подскажите, пожалуйста, с кем лучше обсудить запись клиентов и расписание? Как к человеку обратиться и когда удобно перезвонить?</t>
+          <t>Подскажите, пожалуйста, с кем лучше обсудить онлайн-запись и расписание? Как к человеку обратиться и когда удобно перезвонить?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Фиксируем ФИО, роль, время → перезвон</t>
+          <t>ФИО, роль, время → перезвон</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Если это ЛПР</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2. Уточнение, если клиент на «Дикиди»</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Отлично. У вас буквально две-три минуты? Хочу коротко показать идею и уточнить, как у вас сейчас устроена запись клиентов.</t>
+          <t>Понял(а) вас! Многие клиенты сейчас замечают проблемы с сервисом. Подскажите, вы ещё не сталкивались?</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Если сейчас некогда — договариваемся о перезвоне с конкретным временем</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="108" customHeight="1">
+          <t>Дальше только две ветки: «сталкивались» или «проблем нет»</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2. Короткий рассказ про сервис</t>
+          <t>2А. Если сталкивались с проблемами</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -593,437 +601,214 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — наш сервис для самостоятельной онлайн-записи. Клиент сам выбирает услугу и время — с сайта, из 2ГИС, Яндекс Карт или соцсетей. Можно начать бесплатно на тарифе «Старт»: календарь, онлайн-запись, прайс и до пяти сотрудников — без абонентской платы. Если понадобится больше — подключаете только нужные инструменты или берёте полный тариф.</t>
+          <t>Очень жаль. Из-за текущих обстоятельств малый бизнес действительно страдает. Мы можем предложить помощь и решить вашу проблему с записью.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Не больше 20–25 секунд. Сразу к вопросам</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Переход к вопросам</t>
+          <t>Сразу переходим к этапу 3 — рассказ про бесплатный сервис</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2Б. Если проблем нет</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Расскажите, пожалуйста, как у вас сейчас записываются клиенты?</t>
+          <t>Приятно слышать, что всё хорошо! Буду благодарен(на), если поделитесь обратной связью. Расскажите, какими блоками вы пользуетесь в «Дикиди»? Что в нём вам нравится больше всего?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Открытый вопрос — дальше говорит клиент</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>3. Сбор потребности</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Вопросы</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Что фиксируем</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
+          <t>Слушаем. Фиксируем, что ценят. Затем мягко к этапу 3: «Хочу показать, как у нас устроен бесплатный старт — на всякий случай, как запасной вариант / сравнение»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Доп. вопросы после обратной связи</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>А чего не хватает или что хотелось бы проще?
+Цена «Дикиди» для вас комфортная, или уже смотрите варианты подешевле / без абонентки?</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Боль или «всё ок, но дорого» — мостик к бесплатному Старту</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="108" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>3.1 Как записывают</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Открытый</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Клиенты к вам чаще звонят, пишут в мессенджеры, приходят из соцсетей — или уже есть онлайн-запись?</t>
+          <t>3. Рассказ про бесплатный сервис «Блиц-запись»</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Мы предлагаем сервис «Блиц-запись» — самостоятельная онлайн-запись клиентов. Можно начать бесплатно: календарь, онлайн-запись, прайс, до пяти сотрудников, без абонентской платы. Сервис наш, данные хранятся в Иркутске — рядом поддержка группы компаний «Форус», не «где-то далеко». Подключается к 2ГИС, сайту и соцсетям: клиент записывается сам, администратор меньше сидит на телефоне.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Канал записи</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>3.2 Кто ведёт расписание</t>
-        </is>
-      </c>
+          <t>После рассказа — 1–2 уточняющих вопроса, затем демонстрация</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Открытый</t>
+          <t>Уточнения перед демо</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Кто этим занимается — вы сами, администратор или мастер?</t>
+          <t>Сколько у вас примерно мастеров / сотрудников в записи?
+Онлайн-запись сейчас стоит на сайте, в 2ГИС, в соцсетях — или в основном через администратора?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Кто ЛПР / кто работает с записью</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1">
+          <t>Масштаб и каналы</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="92" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>3.3 Чем пользуются</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Закрытый → открытый</t>
+          <t>4. Тарифы — только если спросили или сравнили с «Дикиди»</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Чем сейчас пользуетесь — тетрадь, таблица, «Юклиентс», «Дикиди» или что-то ещё?
-Если назвали сервис: что в нём удобно, а что мешает или кажется лишним?</t>
+          <t>Начните бесплатно на тарифе «Старт» — 0 ₽ в месяц. Если понадобится больше — подключаете только нужные инструменты: аналитика, зарплата, полная база, Telegram-бот, лояльность. Либо берёте всё сразу в тарифе «Управление» — от 1 900 ₽ в месяц при оплате за год. Для запуска под ключ и бренда есть «Премиум».</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Текущий инструмент и боли</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
+          <t>В холоде не давим полным тарифом — якорь на Старт 0 ₽ и сравнение с платной «Дикиди»</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3.4 Потери заявок</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Открытый</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Бывает, что в час пик клиент не дозванивается, пишет в мессенджер — и запись пропадает? Как часто так бывает?</t>
+          <t>5. Приглашение на демонстрацию</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Давайте я просто покажу, как это выглядит рядом с тем, к чему вы привыкли в «Дикиди». За 15–20 минут пройдёмся по онлайн-записи и бесплатному старту. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Потери и хаос</t>
+          <t>Выбор из двух слотов</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>3.5 Онлайн-запись и каналы</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Закрытый / открытый</t>
+          <t>Если «надо подумать» / «у нас Дикиди, не хотим менять»</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Клиенты могут сами записаться с сайта, из 2ГИС или соцсетей — или всё идёт только через администратора?
-Было бы удобно, если бы запись шла сама, без звонка?</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Готовность к самостоятельной онлайн-записи</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
+          <t>Понимаю, менять привычный сервис непросто. Как раз поэтому предлагаю короткую демонстрацию без обязательств — просто сравните с тем, что есть, особенно бесплатный «Старт». Давайте 15 минут на [день]?</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>3.6 Неявки</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Закрытый → открытый</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Вы напоминаете клиентам о визите?
-Если нет: а неявки сильно бьют по загрузке?</t>
+          <t>Фиксация</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Хорошо. Куда удобнее отправить ссылку — на почту или в мессенджер? Подтверждаем: [дата], [время], демонстрация «Блиц-запись». Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Неявки / напоминания</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
+          <t>Письмо + задача в CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>3.7 Главная боль</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Открытый</t>
+          <t>6. Если демонстрацию не ставят</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Если честно: что в записи и расписании сейчас больше всего отнимает время или нервы?</t>
+          <t>Хорошо, настаивать не буду. Могу скинуть короткое описание — там есть бесплатный «Старт» — и созвониться [день / время], если с «Дикиди» снова будут сложности. Какая почта удобнее?</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Главная боль</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>3.8 Повтор услышанного</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Правильно понимаю: сейчас у вас [как записывают], больше всего мешает [боль], и важно [что хочет получить]. Верно?</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Подтверждение перед презентацией</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>4. Рассказ о «Блиц-записи» под боль клиента</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Правило</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Берём 2–3 пункта из ответов. Прайс целиком не читаем. Акцент — бесплатный старт и самостоятельная онлайн-запись.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Если теряют заявки / много звонков</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Как раз для этого и делали: клиент сам записывается онлайн — с сайта, из 2ГИС, Яндекс Карт, соцсетей. Заявка сразу в календарь, без накладок. Администратор меньше сидит на телефоне.</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Если дорого / не готовы платить сразу</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Можно начать бесплатно: тариф «Старт» — 0 рублей в месяц. Календарь, онлайн-запись, прайс, до пяти сотрудников, один филиал. Абонентской платы нет. Когда понадобится аналитика, зарплата, лояльность или Telegram-бот — подключаете только нужное или берёте полный тариф.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Если путаница в расписании</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Всё расписание в одном месте. Система не даёт задвоить запись. На «Управлении» ещё графики сотрудников и контроль загрузки.</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Если нужна база / возврат клиентов</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>На «Старте» есть база клиентов. Если нужна история визитов, выгрузка, аналитика и система лояльности — это уже в доп. инструментах или в тарифе «Управление».</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Если хотят «всё под ключ» и бренд</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Тогда смотрим «Премиум»: персональный менеджер, брендирование кабинета и страницы записи, размещение в витрине, запуск под ключ, подключение каналов привлечения и аналитика записей из 2ГИС, Яндекс Карт, сайта и соцсетей.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>5. Приглашение на демонстрацию</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Давайте я просто покажу, как это выглядит. За 15–20 минут пройдёмся по онлайн-записи, календарю и бесплатному старту — уже на вашем формате. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Всегда даём выбор из двух вариантов времени</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Если «надо подумать»</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Понимаю. Как раз поэтому и предлагаю короткую демонстрацию — посмотрите глазами, особенно бесплатный «Старт», и уже после будет понятнее. Давайте поставим 15 минут на [день]?</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Фиксация</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Хорошо. Куда удобнее отправить ссылку — на почту или в мессенджер? Подтверждаем: [дата], [время], демонстрация «Блиц-запись», минут 15–20. Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>После звонка: письмо со ссылкой + задача в CRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>6. Если демонстрацию сейчас не ставят</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Говорим</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Хорошо, настаивать не буду. Зафиксирую, что для вас важно: [боль]. Могу скинуть короткое описание тарифов — там есть бесплатный «Старт» — и созвониться [день / время]. Какая почта удобнее?</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Следующий шаг обязателен: письмо / перезвон / материал</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="156" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>На заметку: в холодном звонке не продаём «Управление»/«Премиум» в лоб — ведём через бесплатный старт и демонстрацию; с «Юклиентс»/«Дикиди» не спорим; дольше 40–50 секунд подряд не говорим; цену полного тарифа называем только если спросили.</t>
+          <t>Следующий шаг обязателен</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="140" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>На заметку: не ругаем «Дикиди» в лоб — говорим «многие замечают проблемы» и даём клиенту самому подтвердить. Не спорим, что у них «всё ок». Акцент: бесплатный старт, хранение в Иркутске, поддержка Форус, демонстрация для сравнения.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1036,230 +821,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (новый заход: бесплатный Старт + онлайн-запись)</t>
+          <t>БЫСТРАЯ СХЕМА: клиент сказал «Дикиди»</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+    </row>
+    <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Возражение</t>
+          <t>Шаг</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Что говорим</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Цель</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
+          <t>Текст</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Мне некогда / занят</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Понимаю, не буду долго держать. Предлагаю 15 минут демонстрации — покажу, как выглядит бесплатная онлайн-запись. Когда спокойнее: утро или вечер?</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Слот на демонстрацию</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+          <t>Заход</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Здравствуйте! Меня зовут [имя], группа компаний «Форус». Мы автоматизируем бизнес и онлайн-запись. Звоню по вопросу сотрудничества: предлагаем бесплатный сервис для онлайн-записи. Подскажите, чем вы сейчас пользуетесь?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Нас всё устраивает</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Хорошо, значит процесс уже есть. Часто смотрят «Блиц», чтобы клиент записывался сам с 2ГИС и сайта, а администратор меньше сидел на телефоне. И начать можно бесплатно. Давайте за 15 минут сравните с тем, как у вас сейчас?</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Интерес к бесплатному старту</t>
+          <t>Ответ: «Дикиди»</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Понял(а) вас! Многие клиенты сейчас замечают проблемы с сервисом. Подскажите, вы ещё не сталкивались?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Уже есть другой сервис</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Значит, с онлайн-записью вы уже знакомы. К нам часто приходят из‑за цены и лишнего функционала. У нас можно начать с нуля рублей и подключать только нужное. Могу коротко показать разницу на демонстрации.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Сравнить, не спорить</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="76" customHeight="1">
+          <t>Да, сталкивались</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Очень жаль. Из-за текущих обстоятельств малый бизнес страдает. Мы можем предложить помощь и решить проблему с записью. → Рассказ про бесплатный «Блиц-запись» и хранение в Иркутске → демо.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Это платно / дорого</t>
+          <t>Нет, проблем нет</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Как раз можно начать бесплатно: тариф «Старт» — 0 рублей в месяц. Календарь, онлайн-запись, прайс, до пяти сотрудников. Полный тариф «Управление» — от 1 900 рублей в месяц при оплате за год. На демонстрации покажем оба варианта.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Снять страх цены через Старт 0 ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>Приятно слышать, что всё хорошо! Буду благодарен(на), если поделитесь обратной связью. Какими блоками пользуетесь в «Дикиди»? Что нравится больше всего? → Затем мягко: бесплатный старт для сравнения → демо.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Маленький бизнес / я один</t>
+          <t>Рассказ про сервис</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Для небольшого бизнеса как раз «Старт»: без абонентки, до пяти сотрудников. Если чего-то не хватит — подключаете отдельные инструменты, а не весь пакет сразу.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Подтвердить, что подходит микробизнесу</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>Бесплатный «Старт», самостоятельная онлайн-запись, 2ГИС / сайт / соцсети, данные в Иркутске, поддержка Форус.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Клиенты всё равно звонят</t>
+          <t>Цель</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Часть будет звонить — это нормально. Задача сервиса — забрать тех, кто готов записаться сам с карты, сайта или соцсети. Администраторская запись никуда не девается.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Оба канала вместе</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Нет сайта</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Сайт не обязателен. Онлайн-запись ставят в 2ГИС, Яндекс Карты, соцсети и мессенджер — клиент переходит по ссылке и выбирает время.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Убрать барьер «нужен сайт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Боимся переносить базу / сложно</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>На «Старте» помогаем с переносом и настройкой прайса. На «Премиуме» — запуск под ключ и персональный менеджер. На демонстрации покажем, как это выглядит.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Снять страх внедрения</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Пришлите на почту</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Конечно, направлю. Чтобы не слать лишнее: что сейчас больнее — звонки, неявки или цена текущего сервиса? … И давайте сразу поставим 15 минут — так материал не потеряется. Когда удобно?</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Не оставить только на «пришлите»</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Надо посоветоваться</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Логично. Давайте сразу пригласим партнёра или администратора на демонстрацию. Когда вам обоим удобно?</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Демо с ЛПР и влияющим</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Кто вы такие</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Мы из группы компаний «Форус». «Блиц-запись» — наш сервис онлайн-записи для бизнеса в сфере услуг. Можно начать бесплатно и посмотреть на демонстрации.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Доверие + демо</t>
+          <t>Записать на демонстрацию 15–20 минут.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1271,18 +934,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ТАРИФЫ «БЛИЦ-ЗАПИСЬ» ДЛЯ ХОЛОДНОГО ЗВОНКА  |  Заход: начните бесплатно → нужные инструменты → всё в одном тарифе</t>
+          <t>ВОЗРАЖЕНИЯ — ветка «Дикиди» / сравнение с «Блиц-записью»</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1291,113 +954,142 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Тариф</t>
+          <t>Возражение</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>Что говорим</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Что входит / как говорить</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="124" customHeight="1">
+          <t>Цель</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Старт</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>0 ₽ в месяц</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Всё нужное, чтобы принимать онлайн-записи и вести расписание без абонентской платы.
-Входит: календарь и онлайн-запись; база клиентов без истории и выгрузки; прайс-лист; помощь с переносом и настройкой прайса; до 5 сотрудников; 1 филиал; уведомления PWA и Windows; базовое размещение в витрине партнёров.
-Фраза: «Можно начать бесплатно — без абонентской платы.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="140" customHeight="1">
+          <t>У нас Дикиди, всё устраивает</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Приятно слышать. Многие как раз сравнивают запасной вариант на случай сбоев. У нас можно начать бесплатно и просто посмотреть рядом с тем, к чему привыкли. 15 минут на демонстрацию — когда удобнее?</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Демо без давления сменить сервис</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Модули к «Старту»</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Подключаются отдельно</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Расширяйте тариф под себя — только то, что нужно:
-операционная и финансовая аналитика; график работы сотрудников; автоматический расчёт зарплаты; полная база клиентов с историей, выгрузкой и аналитикой; Telegram-бот с уведомлениями и быстрым управлением записями; система лояльности: скидки, абонементы и сертификаты.
-Фраза: «Не обязательно брать всё сразу — подключаете только нужные инструменты.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="124" customHeight="1">
+          <t>Не хотим переезжать / страшно переносить базу</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Понимаю. На старте помогаем с прайсом и настройкой; данные хранятся в Иркутске, поддержка рядом. На демонстрации покажем, как выглядит переход — без обязательства сразу уходить с «Дикиди».</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Снять страх миграции</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>1 900 ₽/мес при оплате за год
-22 800 ₽ в год
-или 2 100 ₽ при ежемесячной оплате
-Экономия за год — 2 400 ₽</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Весь бизнес в цифрах и под контролем.
-Всё из «Старта» + все доп. инструменты:
-контроль выручки, загрузки и простоев; удалённая аналитика; графики и зарплата; история посещений; лояльность; Telegram-бот.
-Фраза: «Если нужно всё сразу — тариф „Управление“, выгоднее при оплате за год.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="140" customHeight="1">
+          <t>Дикиди дешевле / у нас уже оплачено</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Логично дождаться конца оплаченного периода. «Старт» у нас — 0 ₽, можно подключить параллельно и сравнить. К концу подписки уже будет понятно, оставлять или менять.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Параллельный тест / Старт 0 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Премиум</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2 067 ₽/мес при оплате за год
-24 800 ₽ в год
-или 2 300 ₽ при ежемесячной оплате</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>«Блиц-запись», полностью настроенная под бизнес и бренд.
-Всё из «Управления» + персональный менеджер; полное брендирование кабинета и страницы записи; расширенное XL-размещение в витрине; настройка и запуск под ключ; подключение каналов привлечения; UTM и аналитика записей из 2ГИС, Яндекс Карт, сайта и соцсетей.
-Фраза: «Если нужен запуск под ключ и бренд — смотрим „Премиум“.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="188" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>В холодном звонке опираемся на формулу КП: «Начните бесплатно, подключайте только нужные инструменты или получите все возможности сервиса в одном тарифе.» Детали тарифов — на демонстрации.</t>
+          <t>Проблем с Дикиди не было</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Отлично. Тогда просто поделюсь, чем мы отличаемся: бесплатный старт и хранение в Иркутске. Если когда-нибудь появятся сбои — уже будете знать, к кому обратиться. Могу коротко показать на демонстрации?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Мягкий интерес без давления</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Пришлите на почту</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Конечно. И давайте сразу 15 минут на просмотр — так не потеряется в почте. Когда удобно: завтра до обеда или после?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Письмо + слот</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Дорого (про платные тарифы)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Базовый «Старт» — бесплатно. Полный «Управление» — от 1 900 ₽ в месяц при оплате за год. На демонстрации сравним с тем, что платите сейчас за «Дикиди».</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Якорь на 0 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Некогда</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Не буду долго держать. 15 минут демонстрации в удобный слот — утро или вечер?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Слот</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1409,94 +1101,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПРИМЕРЫ ВНЕДРЕНИЯ — коротко в разговор</t>
+          <t>ТАРИФЫ  |  Для сравнения с «Дикиди»: якорь — бесплатный «Старт», хранение в Иркутске</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Пример</t>
+          <t>Тариф</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Сегмент</t>
+          <t>Цена</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Боль до</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Фраза</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
+          <t>Как говорить</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Салон «Луна»</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Салон красоты</t>
+          <t>Старт</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>0 ₽ в месяц</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Дорогой сервис, лишний функционал</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>«Перенесли базу под ключ, снизили годовые затраты, салон остался на подписке.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
+          <t>Календарь, онлайн-запись, прайс, до 5 сотрудников, 1 филиал, помощь с прайсом, базовое размещение в витрине. Фраза: «Можно начать бесплатно — без абонентки.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Комплекс «Элис»</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Автомойка</t>
+          <t>Модули</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>По необходимости</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Дорого, тяжёлый интерфейс, нужны доработки</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>«Сделали календарь под посты и пик, базу сохранили, дали бонус за переход.»</t>
+          <t>Аналитика, график, зарплата, полная база, Telegram-бот, лояльность. Фраза: «Подключаете только то, чего не хватает.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1 900 ₽/мес за год
+22 800 ₽/год
+или 2 100 ₽ помесячно</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Всё из «Старта» + все модули. Экономия за год — 2 400 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Премиум</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2 067 ₽/мес за год
+24 800 ₽/год
+или 2 300 ₽ помесячно</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Всё из «Управления» + менеджер, брендирование, запуск под ключ, каналы привлечения, аналитика из 2ГИС и соцсетей.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
